--- a/dbbl aug sort.xlsx
+++ b/dbbl aug sort.xlsx
@@ -202,7 +202,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +219,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -259,12 +266,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -818,7 +828,7 @@
       <c r="G4">
         <v>409973949</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="J4" t="s">
@@ -908,5 +918,6 @@
     <sortCondition descending="1" ref="Q1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>